--- a/data/teams_db.xlsx
+++ b/data/teams_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/BravoRanking/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2682" documentId="13_ncr:1_{DC5B1A33-0FFD-42A8-9277-3453C6A8EDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68892BF8-8A69-4B4D-923E-2CF894BAB2DB}"/>
+  <xr:revisionPtr revIDLastSave="2683" documentId="13_ncr:1_{DC5B1A33-0FFD-42A8-9277-3453C6A8EDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBEAC28D-70C2-4E90-930A-E7F3808C539B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35730" yWindow="3570" windowWidth="20370" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1063">
   <si>
     <t>team</t>
   </si>
@@ -3168,6 +3168,60 @@
   </si>
   <si>
     <t>base_def</t>
+  </si>
+  <si>
+    <t>alderney.png</t>
+  </si>
+  <si>
+    <t>ethiopia.png</t>
+  </si>
+  <si>
+    <t>felvidék.png</t>
+  </si>
+  <si>
+    <t>fiji.png</t>
+  </si>
+  <si>
+    <t>gambia.png</t>
+  </si>
+  <si>
+    <t>georgia.png</t>
+  </si>
+  <si>
+    <t>greece.png</t>
+  </si>
+  <si>
+    <t>hungary.png</t>
+  </si>
+  <si>
+    <t>iran.png</t>
+  </si>
+  <si>
+    <t>isle of man.png</t>
+  </si>
+  <si>
+    <t>rwanda.png</t>
+  </si>
+  <si>
+    <t>shetland.png</t>
+  </si>
+  <si>
+    <t>sudan.png</t>
+  </si>
+  <si>
+    <t>székely land.png</t>
+  </si>
+  <si>
+    <t>togo.png</t>
+  </si>
+  <si>
+    <t>western armenia.png</t>
+  </si>
+  <si>
+    <t>western australia.png</t>
+  </si>
+  <si>
+    <t>western isles.png</t>
   </si>
 </sst>
 </file>
@@ -3367,10 +3421,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E0B0BB44-9E7E-43A7-AA99-FFF6C6318EC7}" name="Tableau1" displayName="Tableau1" ref="A1:M594" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A1:M594" xr:uid="{E0B0BB44-9E7E-43A7-AA99-FFF6C6318EC7}"/>
@@ -3382,9 +3432,7 @@
     <tableColumn id="2" xr3:uid="{62257617-C0A4-4915-B189-F9695E8E28AD}" name="team"/>
     <tableColumn id="9" xr3:uid="{FC3B8680-CE03-4F68-8879-2EFE0DC10C51}" name="reference_team"/>
     <tableColumn id="3" xr3:uid="{01DE789D-42BE-463D-88AB-3E344C3FCE8F}" name="tricode" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{A05E0B0F-A814-4781-9CE2-6298B5EC9124}" name="flag" dataDxfId="9">
-      <calculatedColumnFormula>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="11" xr3:uid="{A05E0B0F-A814-4781-9CE2-6298B5EC9124}" name="flag" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{0FD4F960-3B0C-447F-8BC7-5079688D9BD2}" name="confederation"/>
     <tableColumn id="5" xr3:uid="{A520C064-F28A-4290-A89D-AFF5FD6CDC86}" name="startDate" dataDxfId="8"/>
     <tableColumn id="6" xr3:uid="{8D7CB652-1C1A-4A01-BF8A-81C5A74F140A}" name="endDate" dataDxfId="7"/>
@@ -4576,9 +4624,8 @@
       <c r="C23" t="s">
         <v>251</v>
       </c>
-      <c r="E23" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>alderney.png</v>
+      <c r="E23" s="6" t="s">
+        <v>1045</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -6455,9 +6502,8 @@
       <c r="D72" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="E72" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>benin.png</v>
+      <c r="E72" s="6" t="s">
+        <v>627</v>
       </c>
       <c r="F72" t="s">
         <v>460</v>
@@ -7864,9 +7910,8 @@
       <c r="D107" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E107" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>cambodia.png</v>
+      <c r="E107" s="6" t="s">
+        <v>640</v>
       </c>
       <c r="F107" t="s">
         <v>452</v>
@@ -11875,9 +11920,8 @@
       <c r="D209" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E209" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>ethiopia.png</v>
+      <c r="E209" s="6" t="s">
+        <v>1046</v>
       </c>
       <c r="F209" t="s">
         <v>460</v>
@@ -12022,9 +12066,8 @@
       <c r="C213" t="s">
         <v>282</v>
       </c>
-      <c r="E213" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>felvidék.png</v>
+      <c r="E213" s="6" t="s">
+        <v>1047</v>
       </c>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
@@ -12095,9 +12138,8 @@
       <c r="D215" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E215" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>fiji.png</v>
+      <c r="E215" s="6" t="s">
+        <v>1048</v>
       </c>
       <c r="F215" t="s">
         <v>458</v>
@@ -12482,9 +12524,8 @@
       <c r="D226" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E226" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>gambia.png</v>
+      <c r="E226" s="6" t="s">
+        <v>1049</v>
       </c>
       <c r="F226" t="s">
         <v>460</v>
@@ -12604,9 +12645,8 @@
       <c r="D229" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E229" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>georgia.png</v>
+      <c r="E229" s="6" t="s">
+        <v>1050</v>
       </c>
       <c r="F229" t="s">
         <v>443</v>
@@ -12855,9 +12895,8 @@
       <c r="D235" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E235" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>germany.png</v>
+      <c r="E235" s="6" t="s">
+        <v>666</v>
       </c>
       <c r="F235" t="s">
         <v>443</v>
@@ -13360,9 +13399,8 @@
       <c r="D248" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E248" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>greece.png</v>
+      <c r="E248" s="6" t="s">
+        <v>1051</v>
       </c>
       <c r="F248" t="s">
         <v>443</v>
@@ -14449,9 +14487,8 @@
       <c r="D276" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E276" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>hungary.png</v>
+      <c r="E276" s="6" t="s">
+        <v>1052</v>
       </c>
       <c r="F276" t="s">
         <v>443</v>
@@ -14736,9 +14773,8 @@
       <c r="D283" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E283" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>iran.png</v>
+      <c r="E283" s="6" t="s">
+        <v>1053</v>
       </c>
       <c r="F283" t="s">
         <v>452</v>
@@ -15128,9 +15164,8 @@
       <c r="C293" t="s">
         <v>233</v>
       </c>
-      <c r="E293" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>isle of man.png</v>
+      <c r="E293" s="6" t="s">
+        <v>1054</v>
       </c>
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
@@ -20796,9 +20831,8 @@
       <c r="D442" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="E442" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>rwanda.png</v>
+      <c r="E442" s="6" t="s">
+        <v>1055</v>
       </c>
       <c r="F442" t="s">
         <v>460</v>
@@ -21730,9 +21764,8 @@
       <c r="D467" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E467" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>yugoslavia.png</v>
+      <c r="E467" s="6" t="s">
+        <v>783</v>
       </c>
       <c r="F467" t="s">
         <v>443</v>
@@ -22060,9 +22093,8 @@
       <c r="C475" t="s">
         <v>219</v>
       </c>
-      <c r="E475" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>shetland.png</v>
+      <c r="E475" s="6" t="s">
+        <v>1056</v>
       </c>
       <c r="G475" s="4"/>
       <c r="H475" s="4"/>
@@ -23545,9 +23577,8 @@
       <c r="D513" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="E513" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>sudan.png</v>
+      <c r="E513" s="6" t="s">
+        <v>1057</v>
       </c>
       <c r="F513" t="s">
         <v>460</v>
@@ -24103,9 +24134,8 @@
       <c r="C527" t="s">
         <v>280</v>
       </c>
-      <c r="E527" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>székely land.png</v>
+      <c r="E527" s="6" t="s">
+        <v>1058</v>
       </c>
       <c r="G527" s="4"/>
       <c r="H527" s="4"/>
@@ -24619,9 +24649,8 @@
       <c r="D541" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E541" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>togo.png</v>
+      <c r="E541" s="6" t="s">
+        <v>1059</v>
       </c>
       <c r="F541" t="s">
         <v>460</v>
@@ -25914,9 +25943,8 @@
       <c r="C575" t="s">
         <v>285</v>
       </c>
-      <c r="E575" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>western armenia.png</v>
+      <c r="E575" s="6" t="s">
+        <v>1060</v>
       </c>
       <c r="G575" s="4"/>
       <c r="H575" s="4"/>
@@ -25942,9 +25970,8 @@
       <c r="C576" t="s">
         <v>178</v>
       </c>
-      <c r="E576" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>western australia.png</v>
+      <c r="E576" s="6" t="s">
+        <v>1061</v>
       </c>
       <c r="G576" s="4"/>
       <c r="H576" s="4"/>
@@ -25970,9 +25997,8 @@
       <c r="C577" t="s">
         <v>253</v>
       </c>
-      <c r="E577" s="6" t="str">
-        <f>LOWER(Tableau1[[#This Row],[team]])&amp;".png"</f>
-        <v>western isles.png</v>
+      <c r="E577" s="6" t="s">
+        <v>1062</v>
       </c>
       <c r="G577" s="4"/>
       <c r="H577" s="4"/>
@@ -26631,13 +26657,23 @@
       <formula>YEAR(G2)&gt;2000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H438:H1048576 H1:H158 H160:H436">
-    <cfRule type="expression" dxfId="3" priority="5">
+  <conditionalFormatting sqref="G161">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>G161&gt;=F162</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H158 H160:H436 H438:H1048576">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>H1&gt;=G2</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H159">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>YEAR(H159)&gt;2000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H437">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>YEAR(H437)&gt;2000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26651,16 +26687,6 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G161">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>G161&gt;=F162</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H159">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>YEAR(H159)&gt;2000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
